--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104745_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104745_W32.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.979</v>
+        <v>4.8258</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8945</v>
+        <v>3.2413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.5845</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2383</v>
+        <v>1.9348</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4607</v>
+        <v>2.1569</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7776</v>
+        <v>-0.2221</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0802</v>
+        <v>1.5156</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4464</v>
+        <v>1.1958</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6338</v>
+        <v>0.3198</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1581</v>
+        <v>0.4192</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0143</v>
+        <v>0.9611</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1438</v>
+        <v>-0.5419</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2272</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.514</v>
+        <v>0.9397</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9503</v>
+        <v>0.9125</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4363</v>
+        <v>0.0272</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2268</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0913</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0197</v>
+        <v>3.7725</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6694</v>
+        <v>3.5798</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3503</v>
+        <v>0.1927</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9376</v>
+        <v>3.2354</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1586</v>
+        <v>2.456</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.221</v>
+        <v>0.7793</v>
       </c>
       <c r="J3" t="n">
-        <v>1.528</v>
+        <v>2.0702</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2045</v>
+        <v>1.4372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3235</v>
+        <v>0.633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4096</v>
+        <v>1.1652</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0189</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5446</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3631</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1268</v>
+        <v>0.3079</v>
       </c>
       <c r="T3" t="n">
-        <v>0.322</v>
+        <v>0.6478</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1952</v>
+        <v>-0.3399</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1825</v>
+        <v>0.2292</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1825</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2054</v>
+        <v>2.2286</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9112</v>
+        <v>0.7318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2942</v>
+        <v>1.4968</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6856</v>
+        <v>2.5467</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.92</v>
+        <v>1.0247</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9333</v>
+        <v>1.7262</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4726</v>
+        <v>1.6375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4607</v>
+        <v>0.0887</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7523</v>
+        <v>0.8204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.293</v>
+        <v>-0.1155</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4594</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1372</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1134</v>
+        <v>0.1438</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2022</v>
+        <v>-0.0066</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.705</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9294</v>
+        <v>1.9987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1328</v>
+        <v>1.7766</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7967</v>
+        <v>0.2221</v>
       </c>
       <c r="G5" t="n">
-        <v>2.548</v>
+        <v>1.6847</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5215</v>
+        <v>0.7692</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0266</v>
+        <v>0.9156</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7356</v>
+        <v>0.9221</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6417</v>
+        <v>0.4686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0939</v>
+        <v>0.4534</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8125</v>
+        <v>0.7627</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1203</v>
+        <v>0.3005</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9327</v>
+        <v>0.4622</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1642</v>
+        <v>-0.1217</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4669</v>
+        <v>-0.2349</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3026</v>
+        <v>0.1132</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9099</v>
+        <v>1.7855</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3357</v>
+        <v>2.0462</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4258</v>
+        <v>-0.2607</v>
       </c>
       <c r="G6" t="n">
-        <v>1.862</v>
+        <v>1.8634</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6834</v>
       </c>
       <c r="I6" t="n">
-        <v>1.179</v>
+        <v>1.18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6448</v>
+        <v>0.6433</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5703</v>
+        <v>0.5688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2171</v>
+        <v>1.2201</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1127</v>
+        <v>0.1146</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1045</v>
+        <v>1.1055</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4576</v>
+        <v>0.3287</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5996</v>
+        <v>0.3134</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.142</v>
+        <v>0.0152</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7645</v>
+        <v>1.785</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7876</v>
+        <v>0.3335</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5521</v>
+        <v>1.4514</v>
       </c>
       <c r="G7" t="n">
-        <v>2.525</v>
+        <v>2.5313</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7468</v>
+        <v>0.7543</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7782</v>
+        <v>1.7771</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4589</v>
+        <v>1.4512</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1322</v>
+        <v>-0.1346</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5911</v>
+        <v>1.5858</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0661</v>
+        <v>1.0801</v>
       </c>
       <c r="N7" t="n">
-        <v>0.879</v>
+        <v>0.8889</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1871</v>
+        <v>0.1912</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0554</v>
+        <v>-0.0439</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8833</v>
+        <v>0.2481</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1721</v>
+        <v>-0.292</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6359</v>
+        <v>0.2102</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2898</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.654</v>
+        <v>0.2102</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6452</v>
+        <v>0.1579</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3268</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.972</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3843</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1233</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0294</v>
+        <v>0.1579</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7965</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2329</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1359</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1359</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2363</v>
+        <v>0.0523</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8143</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.422</v>
+        <v>0.0523</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2218</v>
+        <v>0.1418</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.458</v>
+        <v>2.9974</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6797</v>
+        <v>-2.8557</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0785</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5598</v>
+        <v>0.3298</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6383</v>
+        <v>-0.9695</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3723</v>
+        <v>1.3811</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9211</v>
+        <v>1.1204</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2935</v>
+        <v>0.2607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2938</v>
+        <v>-2.0207</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6387</v>
+        <v>-0.7906</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3449</v>
+        <v>-1.2301</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.4078</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5437</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4598</v>
+        <v>0.7327</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6222</v>
+        <v>0.5269</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1624</v>
+        <v>0.2058</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1786</v>
+        <v>-0.4446</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-1.1708</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1786</v>
+        <v>0.7261</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1578</v>
+        <v>1.0779</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.5569</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1578</v>
+        <v>2.6348</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.3614</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.9243</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.2857</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1578</v>
+        <v>-0.2835</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1578</v>
+        <v>0.3492</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0208</v>
+        <v>0.8024</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.931</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0208</v>
+        <v>-0.1286</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5409</v>
+        <v>-3.3138</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.124</v>
+        <v>-3.455</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4169</v>
+        <v>0.1412</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1473</v>
+        <v>-3.5403</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1427</v>
+        <v>-1.726</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2901</v>
+        <v>-1.8143</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4271</v>
+        <v>-3.2132</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6913</v>
+        <v>-1.7829</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1183</v>
+        <v>-1.4303</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.3271</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5485</v>
+        <v>0.0568</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1718</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5617</v>
+        <v>-0.2287</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3031</v>
+        <v>-0.0141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2587</v>
+        <v>-0.2146</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6475</v>
+        <v>-3.5854</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0597</v>
+        <v>-2.1789</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4121</v>
+        <v>-1.4065</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5421</v>
+        <v>-3.1474</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7266</v>
+        <v>0.1435</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8155</v>
+        <v>-3.2909</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2078</v>
+        <v>-2.4319</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7791</v>
+        <v>0.6895</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4287</v>
+        <v>-3.1213</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3342</v>
+        <v>-0.7155</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0526</v>
+        <v>-0.546</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3868</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5599</v>
+        <v>0.5133</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6247</v>
+        <v>0.253</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0648</v>
+        <v>0.2603</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1413</v>
+        <v>-5.1827</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7903</v>
+        <v>-5.3486</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.351</v>
+        <v>0.1659</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8993</v>
+        <v>0.8949</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0084</v>
+        <v>3.0095</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1091</v>
+        <v>-2.1146</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3659</v>
+        <v>1.3507</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5576</v>
+        <v>2.5511</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1917</v>
+        <v>-1.2004</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4666</v>
+        <v>-0.4558</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4507</v>
+        <v>0.4584</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6797</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.0428</v>
+        <v>-7.0566</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8153</v>
+        <v>0.1579</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1134</v>
+        <v>0.3573</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7019</v>
+        <v>-0.1994</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.514499999999996</v>
+        <v>4.2216</v>
       </c>
       <c r="E14" t="n">
-        <v>2.013799999999999</v>
+        <v>2.553299999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5005</v>
+        <v>1.668</v>
       </c>
       <c r="G14" t="n">
-        <v>8.597500000000002</v>
+        <v>8.599699999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>8.527699999999999</v>
+        <v>8.541700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06979999999999942</v>
+        <v>0.05799999999999894</v>
       </c>
       <c r="J14" t="n">
-        <v>6.868399999999999</v>
+        <v>6.776699999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8753</v>
+        <v>6.827100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.006600000000000161</v>
+        <v>-0.05040000000000089</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7292</v>
+        <v>1.823</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6524</v>
+        <v>1.7145</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07669999999999977</v>
+        <v>0.1084999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.6797</v>
+        <v>-5.690700000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.903</v>
+        <v>-15.9342</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2234</v>
+        <v>10.2436</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8711</v>
+        <v>3.577800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4098</v>
+        <v>4.0848</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5388000000000002</v>
+        <v>-0.5071</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2745</v>
+        <v>-2.2653</v>
       </c>
       <c r="W14" t="n">
-        <v>7.638999999999999</v>
+        <v>7.626399999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.913200000000002</v>
+        <v>-9.891500000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.646</v>
+        <v>4.7878</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8052</v>
+        <v>3.8309</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8408</v>
+        <v>0.9569</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0562</v>
+        <v>1.0504</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3525</v>
+        <v>0.3405</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7037</v>
+        <v>0.7099</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6917</v>
+        <v>1.6746</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9298</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7456</v>
+        <v>0.7447</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6355</v>
+        <v>-0.6241</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5936</v>
+        <v>-0.5893</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0419</v>
+        <v>-0.0348</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>1.817</v>
+        <v>0.965</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5213</v>
+        <v>0.5708</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2957</v>
+        <v>0.3942</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6539</v>
+        <v>4.3583</v>
       </c>
       <c r="E16" t="n">
-        <v>3.883</v>
+        <v>3.501</v>
       </c>
       <c r="F16" t="n">
-        <v>0.771</v>
+        <v>0.8572</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4642</v>
+        <v>1.464</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1262</v>
+        <v>-1.1283</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5904</v>
+        <v>2.5923</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3094</v>
+        <v>3.2947</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5193</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7901</v>
+        <v>2.7851</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8452</v>
+        <v>-1.8307</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6455</v>
+        <v>-1.638</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1997</v>
+        <v>-0.1927</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="T16" t="n">
-        <v>0.663</v>
+        <v>0.3037</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1101</v>
+        <v>-0.0436</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9963</v>
+        <v>2.3044</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5556</v>
+        <v>1.6665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4408</v>
+        <v>0.6379</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9222</v>
+        <v>2.9233</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9317</v>
+        <v>0.9331</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9906</v>
+        <v>1.9902</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8647</v>
+        <v>1.8596</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8641</v>
+        <v>0.8618</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0006</v>
+        <v>0.9977</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0575</v>
+        <v>1.0638</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="O17" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3802</v>
+        <v>-1.0742</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3091</v>
+        <v>-0.193</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0711</v>
+        <v>-0.8812</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4866</v>
+        <v>0.733</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0823</v>
+        <v>-0.1055</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5689</v>
+        <v>0.8385</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9351</v>
+        <v>-2.9372</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.7326</v>
+        <v>-3.7358</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7976</v>
+        <v>0.7986</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8423</v>
+        <v>-2.8565</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.9362</v>
+        <v>-2.9452</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0939</v>
+        <v>0.0887</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0806</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7037</v>
+        <v>0.7099</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3511</v>
+        <v>-1.1022</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0319</v>
+        <v>0.0273</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.383</v>
+        <v>-1.1295</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,19 +1891,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1849</v>
+        <v>-0.9124</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8748</v>
+        <v>1.9158</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0597</v>
+        <v>-2.8282</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1747</v>
+        <v>0.1766</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0195</v>
+        <v>0.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1551</v>
+        <v>0.1566</v>
       </c>
       <c r="J20" t="n">
-        <v>0.74</v>
+        <v>0.7355</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6282</v>
+        <v>0.6238</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5654</v>
+        <v>-0.5588</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0433</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1097</v>
+        <v>-0.8386</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1109</v>
+        <v>0.1623</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2206</v>
+        <v>-1.0009</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1587</v>
+        <v>-1.1609</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0238</v>
+        <v>1.018</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7782</v>
+        <v>-1.1516</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8021</v>
+        <v>-0.225</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9761</v>
+        <v>-0.9266</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5253</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2636</v>
+        <v>0.262</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1696</v>
+        <v>0.1586</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1503</v>
+        <v>0.1444</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0193</v>
+        <v>0.0142</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6949</v>
+        <v>-0.6863</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9392</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6607</v>
+        <v>-0.0384</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9717</v>
+        <v>-0.3836</v>
       </c>
       <c r="U21" t="n">
-        <v>0.311</v>
+        <v>0.3452</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7116</v>
+        <v>-2.1987</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7276</v>
+        <v>-1.2576</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9839</v>
+        <v>-0.9411</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6382</v>
+        <v>-2.634</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5944</v>
+        <v>-1.5914</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0439</v>
+        <v>-1.0426</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3996</v>
+        <v>-1.4014</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6852</v>
+        <v>-0.6862</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2387</v>
+        <v>-1.2326</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9092</v>
+        <v>-0.9052</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.118</v>
+        <v>0.3867</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3281</v>
+        <v>0.1438</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2101</v>
+        <v>0.2429</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0902</v>
+        <v>-2.7616</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4442</v>
+        <v>-3.2162</v>
       </c>
       <c r="F23" t="n">
-        <v>0.354</v>
+        <v>0.4547</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4392</v>
+        <v>-1.4399</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2555</v>
+        <v>-1.255</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1837</v>
+        <v>-0.1849</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9108</v>
+        <v>-1.9153</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.526</v>
+        <v>-1.5276</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3848</v>
+        <v>-0.3877</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4715</v>
+        <v>0.4754</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2705</v>
+        <v>0.2725</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9694</v>
+        <v>-0.6388</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3975</v>
+        <v>-0.1628</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5719</v>
+        <v>-0.476</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0272</v>
+        <v>-3.4012</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2331</v>
+        <v>-2.7814</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7941</v>
+        <v>-0.6197</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.897</v>
+        <v>-0.8972</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4884</v>
+        <v>0.4882</v>
       </c>
       <c r="I24" t="n">
         <v>-1.3854</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3488</v>
+        <v>-0.3585</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4208</v>
+        <v>0.4169</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7696</v>
+        <v>-0.7754</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5482</v>
+        <v>-0.5387</v>
       </c>
       <c r="N24" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6158</v>
+        <v>-0.61</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3127</v>
+        <v>-0.6829</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5678</v>
+        <v>-0.098</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7449</v>
+        <v>-0.5849</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3325</v>
+        <v>-4.3205</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3297</v>
+        <v>-4.9964</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9972</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.607</v>
+        <v>-5.6058</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6492</v>
+        <v>-1.651</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.9578</v>
+        <v>-3.9548</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0029</v>
+        <v>-3.0143</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0337</v>
+        <v>-0.042</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.9692</v>
+        <v>-2.9724</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.604</v>
+        <v>-2.5915</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6154</v>
+        <v>-1.6091</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9886</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6607</v>
+        <v>0.6723</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2143</v>
+        <v>0.1365</v>
       </c>
       <c r="U25" t="n">
-        <v>0.875</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.514599999999997</v>
+        <v>-2.734899999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5004</v>
+        <v>-1.667900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0139</v>
+        <v>-1.0669</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.597300000000001</v>
+        <v>-8.5999</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.5275</v>
+        <v>-8.541699999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.06979999999999942</v>
+        <v>-0.05809999999999915</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.729</v>
+        <v>-1.823</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6523</v>
+        <v>-1.7147</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.07659999999999911</v>
+        <v>-0.1085999999999996</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.8685</v>
+        <v>-6.7765</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.875100000000001</v>
+        <v>-6.827199999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.006899999999999906</v>
+        <v>0.05039999999999989</v>
       </c>
       <c r="P26" t="n">
-        <v>5.6796</v>
+        <v>5.6909</v>
       </c>
       <c r="Q26" t="n">
-        <v>-10.2234</v>
+        <v>-10.2435</v>
       </c>
       <c r="R26" t="n">
-        <v>15.903</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.8712</v>
+        <v>-2.0911</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5386000000000002</v>
+        <v>0.5070000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.4098</v>
+        <v>-2.598</v>
       </c>
       <c r="V26" t="n">
-        <v>2.274399999999999</v>
+        <v>2.265300000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>9.9132</v>
+        <v>9.891599999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.638900000000001</v>
+        <v>-7.626300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104745_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104745_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.891500000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104745_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.626300000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
